--- a/excel/catboost_train_fixed_v3/catboost_train_05_10rows_6groups_fixed.xlsx
+++ b/excel/catboost_train_fixed_v3/catboost_train_05_10rows_6groups_fixed.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Для_разметки_CatBoost" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарии_не_признаки" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Для_разметки_CatBoost" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Сценарии_не_признаки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Инструкция" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Для_разметки_CatBoost'!$A$1:$AA$11</definedName>
@@ -669,7 +669,7 @@
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>founders_common_persons</t>
+          <t>founders_common_count</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>directors_common_persons</t>
+          <t>directors_common_count</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
@@ -1743,7 +1743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1773,6 +1773,46 @@
           <t>Сценарий (не признак модели)</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>founders_search_completed</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>founders_candidate_found</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>founders_common_count</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>founders_basis_count</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>directors_search_completed</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>directors_candidate_found</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>directors_common_count</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>directors_basis_count</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1795,6 +1835,30 @@
           <t>Сильный многокритериальный профиль; учебный подтвержденный случай.</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1817,6 +1881,30 @@
           <t>Неоднозначный профиль: одинаковые наблюдаемые признаки встречаются с обеими метками; исход задан учебным сценарием.</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1839,6 +1927,30 @@
           <t>Сильный многокритериальный профиль; учебный подтвержденный случай.</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1861,6 +1973,30 @@
           <t>Неоднозначный профиль: одинаковые наблюдаемые признаки встречаются с обеими метками; исход задан учебным сценарием.</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1883,6 +2019,30 @@
           <t>Сильный многокритериальный профиль; учебный подтвержденный случай.</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1905,6 +2065,30 @@
           <t>Неоднозначный профиль: одинаковые наблюдаемые признаки встречаются с обеими метками; исход задан учебным сценарием.</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1927,6 +2111,30 @@
           <t>Сильный многокритериальный профиль; учебный подтвержденный случай.</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1949,6 +2157,30 @@
           <t>Неоднозначный профиль: одинаковые наблюдаемые признаки встречаются с обеими метками; исход задан учебным сценарием.</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1971,6 +2203,30 @@
           <t>Слабая изолированная связь; учебный отрицательный случай, не автоматическое правило для реальной разметки.</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1992,6 +2248,30 @@
         <is>
           <t>Слабая изолированная связь; учебный отрицательный случай, не автоматическое правило для реальной разметки.</t>
         </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2006,7 +2286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2024,6 +2304,46 @@
           <t>Пояснение</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>founders_search_completed</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>founders_candidate_found</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>founders_common_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>founders_basis_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>directors_search_completed</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>directors_candidate_found</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>directors_common_count</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>directors_basis_count</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -2036,6 +2356,30 @@
           <t>СИНТЕТИЧЕСКИЙ учебный набор. Не применять для оценки реального качества или принятия решений.</t>
         </is>
       </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" ht="48" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -2048,6 +2392,30 @@
           <t>10 строк данных, 6 независимых компонент по ИНН. Размеры групп: 2, 2, 2, 2, 1, 1. Заголовок не считается строкой данных.</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" ht="48" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -2060,6 +2428,30 @@
           <t>Загружать лист Для_разметки_CatBoost через функцию обучения на признаках. Если выбирается один файл, объедините основные листы без повторных заголовков.</t>
         </is>
       </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -2072,6 +2464,30 @@
           <t>24 числовых столбца. source_inn и candidate_inn — только идентификаторы и группировка. Метка и лист сценариев не являются признаками.</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="48" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -2084,6 +2500,30 @@
           <t>1/0 — заранее заданные исходы вымышленных сценариев, не экспертная проверка реальных организаций.</t>
         </is>
       </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" ht="48" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -2096,6 +2536,30 @@
           <t>Профиль, похожий на 9900000031, имеет одинаковые числовые признаки с разными метками. Это намеренная учебная неоднозначность, а не инструкция так размечать реальные случаи.</t>
         </is>
       </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -2108,6 +2572,30 @@
           <t>Для demo_transition желаемые оценки: 9900000024 — от 0.7 до 1; 9900000031 — строго между 0.3 и 0.7. Это демонстрационная цель, не гарантия при любых настройках.</t>
         </is>
       </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -2120,6 +2608,30 @@
           <t>Демонстрационные кандидаты не включены под своими ИНН в обучение. Их профили использованы при проектировании синтетического набора; это не независимый тест.</t>
         </is>
       </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -2132,6 +2644,30 @@
           <t>Группы по связным компонентам ИНН; не разбивать строки одной группы между train/validation/test. После разбиения проверить оба класса в каждой части.</t>
         </is>
       </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -2144,6 +2680,30 @@
           <t>Названия признаков соответствуют доступной выгрузке кандидатов. Совместимость с актуальным загрузчиком и его настройками без исходников не подтверждена.</t>
         </is>
       </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2155,6 +2715,30 @@
         <is>
           <t>period_start=2025-01-01; period_end=2025-12-31. Условный период синтетических примеров; не восстановлен из реальных документов. ИНН, признаки и метки исходного архива не изменены.</t>
         </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
